--- a/artfynd/A 46807-2024 artfynd.xlsx
+++ b/artfynd/A 46807-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110595</v>
+        <v>121111270</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>90468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nytorp, Nytorp, Upl</t>
+          <t>Adamsberg, Adamsberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699601</v>
+        <v>699829</v>
       </c>
       <c r="R2" t="n">
-        <v>6623095</v>
+        <v>6623289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111270</v>
+        <v>121111225</v>
       </c>
       <c r="B3" t="n">
-        <v>90458</v>
+        <v>98830</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>222361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699829</v>
+        <v>699819</v>
       </c>
       <c r="R3" t="n">
-        <v>6623289</v>
+        <v>6623296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110654</v>
+        <v>121110595</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699624</v>
+        <v>699601</v>
       </c>
       <c r="R4" t="n">
-        <v>6623159</v>
+        <v>6623095</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111102</v>
+        <v>121110654</v>
       </c>
       <c r="B5" t="n">
-        <v>91959</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Adamsberg, Adamsberg, Upl</t>
+          <t>Nytorp, Nytorp, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699767</v>
+        <v>699624</v>
       </c>
       <c r="R5" t="n">
-        <v>6623353</v>
+        <v>6623159</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111225</v>
+        <v>121111102</v>
       </c>
       <c r="B6" t="n">
-        <v>98820</v>
+        <v>91969</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222361</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699819</v>
+        <v>699767</v>
       </c>
       <c r="R6" t="n">
-        <v>6623296</v>
+        <v>6623353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>121110903</v>
       </c>
       <c r="B7" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 46807-2024 artfynd.xlsx
+++ b/artfynd/A 46807-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111225</v>
+        <v>121110654</v>
       </c>
       <c r="B3" t="n">
-        <v>98830</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Adamsberg, Adamsberg, Upl</t>
+          <t>Nytorp, Nytorp, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699819</v>
+        <v>699624</v>
       </c>
       <c r="R3" t="n">
-        <v>6623296</v>
+        <v>6623159</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110595</v>
+        <v>121111225</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>98830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nytorp, Nytorp, Upl</t>
+          <t>Adamsberg, Adamsberg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699601</v>
+        <v>699819</v>
       </c>
       <c r="R4" t="n">
-        <v>6623095</v>
+        <v>6623296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121110654</v>
+        <v>121110595</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>100347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699624</v>
+        <v>699601</v>
       </c>
       <c r="R5" t="n">
-        <v>6623159</v>
+        <v>6623095</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 46807-2024 artfynd.xlsx
+++ b/artfynd/A 46807-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111270</v>
+        <v>121111102</v>
       </c>
       <c r="B2" t="n">
-        <v>90468</v>
+        <v>91981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699829</v>
+        <v>699767</v>
       </c>
       <c r="R2" t="n">
-        <v>6623289</v>
+        <v>6623353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110654</v>
+        <v>121111270</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>90480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nytorp, Nytorp, Upl</t>
+          <t>Adamsberg, Adamsberg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699624</v>
+        <v>699829</v>
       </c>
       <c r="R3" t="n">
-        <v>6623159</v>
+        <v>6623289</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121111225</v>
       </c>
       <c r="B4" t="n">
-        <v>98830</v>
+        <v>98843</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121110595</v>
       </c>
       <c r="B5" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111102</v>
+        <v>121110654</v>
       </c>
       <c r="B6" t="n">
-        <v>91969</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Adamsberg, Adamsberg, Upl</t>
+          <t>Nytorp, Nytorp, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699767</v>
+        <v>699624</v>
       </c>
       <c r="R6" t="n">
-        <v>6623353</v>
+        <v>6623159</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>121110903</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 46807-2024 artfynd.xlsx
+++ b/artfynd/A 46807-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111102</v>
+        <v>121111270</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>90481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699767</v>
+        <v>699829</v>
       </c>
       <c r="R2" t="n">
-        <v>6623353</v>
+        <v>6623289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111270</v>
+        <v>121111102</v>
       </c>
       <c r="B3" t="n">
-        <v>90480</v>
+        <v>91982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699829</v>
+        <v>699767</v>
       </c>
       <c r="R3" t="n">
-        <v>6623289</v>
+        <v>6623353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121111225</v>
       </c>
       <c r="B4" t="n">
-        <v>98843</v>
+        <v>98844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121110595</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>121110903</v>
       </c>
       <c r="B7" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 46807-2024 artfynd.xlsx
+++ b/artfynd/A 46807-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121111270</v>
       </c>
       <c r="B2" t="n">
-        <v>90481</v>
+        <v>90484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111102</v>
+        <v>121111225</v>
       </c>
       <c r="B3" t="n">
-        <v>91982</v>
+        <v>98847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>222361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699767</v>
+        <v>699819</v>
       </c>
       <c r="R3" t="n">
-        <v>6623353</v>
+        <v>6623296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111225</v>
+        <v>121110654</v>
       </c>
       <c r="B4" t="n">
-        <v>98844</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222361</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Adamsberg, Adamsberg, Upl</t>
+          <t>Nytorp, Nytorp, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699819</v>
+        <v>699624</v>
       </c>
       <c r="R4" t="n">
-        <v>6623296</v>
+        <v>6623159</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121110595</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121110654</v>
+        <v>121111102</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nytorp, Nytorp, Upl</t>
+          <t>Adamsberg, Adamsberg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699624</v>
+        <v>699767</v>
       </c>
       <c r="R6" t="n">
-        <v>6623159</v>
+        <v>6623353</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>121110903</v>
       </c>
       <c r="B7" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 46807-2024 artfynd.xlsx
+++ b/artfynd/A 46807-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110654</v>
+        <v>121111102</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nytorp, Nytorp, Upl</t>
+          <t>Adamsberg, Adamsberg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699624</v>
+        <v>699767</v>
       </c>
       <c r="R4" t="n">
-        <v>6623159</v>
+        <v>6623353</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121110595</v>
+        <v>121110654</v>
       </c>
       <c r="B5" t="n">
-        <v>100364</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699601</v>
+        <v>699624</v>
       </c>
       <c r="R5" t="n">
-        <v>6623095</v>
+        <v>6623159</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111102</v>
+        <v>121110595</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Adamsberg, Adamsberg, Upl</t>
+          <t>Nytorp, Nytorp, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699767</v>
+        <v>699601</v>
       </c>
       <c r="R6" t="n">
-        <v>6623353</v>
+        <v>6623095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
